--- a/dataset_t6_grouped/results2/G4/G4_T8482_W0038F0003T0006Z000C1N14_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T8482_W0038F0003T0006Z000C1N14_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>31.27260130461513</v>
+        <v>5.081797711999958</v>
       </c>
       <c r="D2" t="n">
-        <v>31.89513432414038</v>
+        <v>5.182959327672813</v>
       </c>
       <c r="E2" t="n">
-        <v>14.90904101224901</v>
+        <v>2.422719164490464</v>
       </c>
       <c r="F2" t="n">
-        <v>14.80777477631072</v>
+        <v>2.406263401150492</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>7.781885857855324</v>
+        <v>1.26455645190149</v>
       </c>
       <c r="D3" t="n">
-        <v>7.15641094642265</v>
+        <v>1.162916778793681</v>
       </c>
       <c r="E3" t="n">
-        <v>14.90904101224901</v>
+        <v>2.422719164490464</v>
       </c>
       <c r="F3" t="n">
-        <v>14.80777477631072</v>
+        <v>2.406263401150492</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>55.87662552155587</v>
+        <v>9.079951647252829</v>
       </c>
       <c r="D4" t="n">
-        <v>56.31084159718846</v>
+        <v>9.150511759543125</v>
       </c>
       <c r="E4" t="n">
-        <v>14.90904101224901</v>
+        <v>2.422719164490464</v>
       </c>
       <c r="F4" t="n">
-        <v>14.80777477631072</v>
+        <v>2.406263401150492</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>26.49355180077942</v>
+        <v>4.305202167626655</v>
       </c>
       <c r="D5" t="n">
-        <v>26.4284330432016</v>
+        <v>4.294620369520261</v>
       </c>
       <c r="E5" t="n">
-        <v>14.90904101224901</v>
+        <v>2.422719164490464</v>
       </c>
       <c r="F5" t="n">
-        <v>14.80777477631072</v>
+        <v>2.406263401150492</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>28.95976931782336</v>
+        <v>4.705962514146297</v>
       </c>
       <c r="D6" t="n">
-        <v>29.21098853904752</v>
+        <v>4.746785637595222</v>
       </c>
       <c r="E6" t="n">
-        <v>14.90904101224901</v>
+        <v>2.422719164490464</v>
       </c>
       <c r="F6" t="n">
-        <v>14.80777477631072</v>
+        <v>2.406263401150492</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>43.80803899025073</v>
+        <v>7.118806335915743</v>
       </c>
       <c r="D7" t="n">
-        <v>44.65881018921402</v>
+        <v>7.257056655747279</v>
       </c>
       <c r="E7" t="n">
-        <v>14.90904101224901</v>
+        <v>2.422719164490464</v>
       </c>
       <c r="F7" t="n">
-        <v>14.80777477631072</v>
+        <v>2.406263401150492</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>32.44512811345108</v>
+        <v>5.2723333184358</v>
       </c>
       <c r="D8" t="n">
-        <v>11.27888617866242</v>
+        <v>1.832819004032643</v>
       </c>
       <c r="E8" t="n">
-        <v>14.90904101224901</v>
+        <v>2.422719164490464</v>
       </c>
       <c r="F8" t="n">
-        <v>14.80777477631072</v>
+        <v>2.406263401150492</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>30.24563793256278</v>
+        <v>4.914916164041451</v>
       </c>
       <c r="D9" t="n">
-        <v>28.88332294059727</v>
+        <v>4.693539977847057</v>
       </c>
       <c r="E9" t="n">
-        <v>14.90904101224901</v>
+        <v>2.422719164490464</v>
       </c>
       <c r="F9" t="n">
-        <v>14.80777477631072</v>
+        <v>2.406263401150492</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>39.95359304569115</v>
+        <v>6.492458869924812</v>
       </c>
       <c r="D10" t="n">
-        <v>6.464411731076432</v>
+        <v>1.05046690629992</v>
       </c>
       <c r="E10" t="n">
-        <v>14.90904101224901</v>
+        <v>2.422719164490464</v>
       </c>
       <c r="F10" t="n">
-        <v>14.80777477631072</v>
+        <v>2.406263401150492</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>38.96570324089201</v>
+        <v>6.331926776644952</v>
       </c>
       <c r="D11" t="n">
-        <v>37.74211281298479</v>
+        <v>6.133093332110029</v>
       </c>
       <c r="E11" t="n">
-        <v>14.90904101224901</v>
+        <v>2.422719164490464</v>
       </c>
       <c r="F11" t="n">
-        <v>14.80777477631072</v>
+        <v>2.406263401150492</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>67.05774562631038</v>
+        <v>10.89688366427544</v>
       </c>
       <c r="D12" t="n">
-        <v>34.66288681030541</v>
+        <v>5.632719106674629</v>
       </c>
       <c r="E12" t="n">
-        <v>14.90904101224901</v>
+        <v>2.422719164490464</v>
       </c>
       <c r="F12" t="n">
-        <v>14.80777477631072</v>
+        <v>2.406263401150492</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
